--- a/data/login.xlsx
+++ b/data/login.xlsx
@@ -3,20 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sreya Basu\eclipse-workspace\SITSeleniumPrograms\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32B07EA-F388-46AE-AE40-FBB942136011}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{0BAB0A82-8CE7-4EDD-AEBF-8BDF8CFC9D20}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16335" windowHeight="4550" xr2:uid="{F50F593E-D585-433F-86DD-7194B8225BE1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17637" windowHeight="3594" activeTab="1" xr2:uid="{F50F593E-D585-433F-86DD-7194B8225BE1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
+  <oleSize ref="A1:P10"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -80,7 +76,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -98,6 +97,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -120,16 +126,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -540,33 +549,34 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{884809A4-5F6F-43E0-9012-726C0C87098E}">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>

--- a/data/login.xlsx
+++ b/data/login.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{0BAB0A82-8CE7-4EDD-AEBF-8BDF8CFC9D20}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{FDD34972-8260-49A8-824B-8AFABBA9DCC2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17637" windowHeight="3594" activeTab="1" xr2:uid="{F50F593E-D585-433F-86DD-7194B8225BE1}"/>
   </bookViews>
